--- a/data/gas_upload_template.xlsx
+++ b/data/gas_upload_template.xlsx
@@ -426,26 +426,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Billing Month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Utility Account</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Therms</t>
         </is>
@@ -462,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -484,58 +490,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Utility Account</t>
+          <t>Billing Month</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Required. Enter the TECO, Gas South, or other utility account number exactly as registered in the dashboard.</t>
+          <t>Required. Enter the billing month as a date, preferably the first day of the month (for example 8/1/2026).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Utility Account</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Required. Total invoice cost in dollars for that utility account for the selected month.</t>
+          <t>Required. Enter the TECO, Gas South, or other utility account number exactly as registered in the dashboard.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Therms</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Required. Therms shown on the invoice. Enter 0 when there is no usage but a fixed charge remains.</t>
+          <t>Required. Total invoice cost in dollars for that utility account and billing month.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gas Bill Month</t>
+          <t>Therms</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Do not add this as a spreadsheet column. Select the month in the Streamlit sidebar before uploading.</t>
+          <t>Required. Therms shown on the invoice. Enter 0 when there is no usage but a fixed charge remains.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Monthly Update</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Append each new month to the bottom of this same workbook. Keep all prior months and re-upload the full file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Account Mapping</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Provider, building, meter, rate, end use, and TECO/Gas South pairing are looked up automatically from Reference Data &gt; Gas Accounts.</t>
         </is>
